--- a/AAII_Financials/Yearly/AIQUY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AIQUY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
   <si>
     <t>AIQUY</t>
   </si>
@@ -972,10 +972,10 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>25485400</v>
+        <v>25525100</v>
       </c>
       <c r="E17" s="3">
-        <v>22673600</v>
+        <v>22708100</v>
       </c>
       <c r="F17" s="3">
         <v>25211200</v>
@@ -1005,10 +1005,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>6145700</v>
+        <v>6106000</v>
       </c>
       <c r="E18" s="3">
-        <v>5339500</v>
+        <v>5304900</v>
       </c>
       <c r="F18" s="3">
         <v>5304500</v>
@@ -1053,10 +1053,10 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-291500</v>
+        <v>-331200</v>
       </c>
       <c r="E20" s="3">
-        <v>-115700</v>
+        <v>-150300</v>
       </c>
       <c r="F20" s="3">
         <v>-37900</v>
@@ -1449,10 +1449,10 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>291500</v>
+        <v>331200</v>
       </c>
       <c r="E32" s="3">
-        <v>115700</v>
+        <v>150300</v>
       </c>
       <c r="F32" s="3">
         <v>37900</v>
@@ -1681,8 +1681,8 @@
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>35</v>
+      <c r="D42" s="3">
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>300</v>
@@ -1781,7 +1781,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1428100</v>
+        <v>1426700</v>
       </c>
       <c r="E45" s="3">
         <v>999700</v>
